--- a/Assets/Data/SourceTables/日常系统.xlsx
+++ b/Assets/Data/SourceTables/日常系统.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\A1\schoolA\Assets\Data\SourceTables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\K\school\Assets\Data\SourceTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09FE8629-A6B6-4ABD-BC36-9241B198EED8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55D10C55-E74A-4D56-919E-2035D57BBA57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3105" yWindow="4740" windowWidth="38700" windowHeight="15435" tabRatio="694" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32085" yWindow="2280" windowWidth="21600" windowHeight="11295" tabRatio="694" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="日程系统" sheetId="1" r:id="rId1"/>
-    <sheet name="NPC位置" sheetId="2" r:id="rId2"/>
-    <sheet name="剧情" sheetId="3" r:id="rId3"/>
+    <sheet name="事件" sheetId="4" r:id="rId2"/>
+    <sheet name="NPC位置" sheetId="2" r:id="rId3"/>
+    <sheet name="剧情" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="32">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -146,6 +147,14 @@
   </si>
   <si>
     <t>女主B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>事件类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NPC</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -486,24 +495,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AF3"/>
+  <dimension ref="A1:AL3"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.25" customWidth="1"/>
-    <col min="5" max="7" width="10.875" customWidth="1"/>
-    <col min="10" max="10" width="11.25" customWidth="1"/>
-    <col min="11" max="12" width="10.875" customWidth="1"/>
-    <col min="17" max="17" width="13.5" customWidth="1"/>
-    <col min="20" max="20" width="11.5" customWidth="1"/>
-    <col min="21" max="21" width="13.625" customWidth="1"/>
-    <col min="22" max="22" width="14.5" customWidth="1"/>
-    <col min="27" max="27" width="11.75" customWidth="1"/>
-    <col min="30" max="30" width="11.25" customWidth="1"/>
-    <col min="31" max="31" width="10.625" customWidth="1"/>
-    <col min="32" max="32" width="11" customWidth="1"/>
+    <col min="5" max="8" width="10.875" customWidth="1"/>
+    <col min="11" max="11" width="11.25" customWidth="1"/>
+    <col min="12" max="14" width="10.875" customWidth="1"/>
+    <col min="19" max="20" width="13.5" customWidth="1"/>
+    <col min="23" max="23" width="11.5" customWidth="1"/>
+    <col min="24" max="24" width="13.625" customWidth="1"/>
+    <col min="25" max="26" width="14.5" customWidth="1"/>
+    <col min="31" max="32" width="11.75" customWidth="1"/>
+    <col min="35" max="35" width="11.25" customWidth="1"/>
+    <col min="36" max="36" width="10.625" customWidth="1"/>
+    <col min="37" max="38" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -525,83 +534,101 @@
       <c r="G1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="O1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="T1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="U1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="V1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="W1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="X1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="Y1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="Z1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="AB1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="AC1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="AD1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AE1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AF1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AG1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AH1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AI1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AE1" s="3" t="s">
+      <c r="AJ1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AK1" s="3" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AL1" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1001</v>
       </c>
@@ -623,26 +650,26 @@
       <c r="G2">
         <v>900003</v>
       </c>
-      <c r="H2" s="1">
+      <c r="I2" s="1">
         <v>0.63541666666666663</v>
       </c>
-      <c r="J2">
+      <c r="K2">
         <v>20001</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>900001</v>
       </c>
-      <c r="L2">
+      <c r="M2">
         <v>900004</v>
       </c>
-      <c r="M2" s="1">
+      <c r="O2" s="1">
         <v>0.84375</v>
       </c>
-      <c r="O2">
+      <c r="Q2">
         <v>20001</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1002</v>
       </c>
@@ -656,18 +683,18 @@
         <v>9</v>
       </c>
       <c r="E3">
+        <v>20001</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0.67708333333333304</v>
+      </c>
+      <c r="K3">
         <v>20002</v>
       </c>
-      <c r="H3" s="1">
-        <v>0.67708333333333304</v>
-      </c>
-      <c r="J3">
-        <v>20002</v>
-      </c>
-      <c r="M3" s="1">
+      <c r="O3" s="1">
         <v>0.88541666666666696</v>
       </c>
-      <c r="O3">
+      <c r="Q3">
         <v>20002</v>
       </c>
     </row>
@@ -678,6 +705,55 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC6E8279-47C2-484A-9180-5D2C5815475F}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="4" max="4" width="13.5" customWidth="1"/>
+    <col min="5" max="5" width="12.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>50001</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2">
+        <v>900001</v>
+      </c>
+      <c r="E2">
+        <v>900003</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D369CECC-53DA-4627-B58F-8141DA65BED6}">
   <dimension ref="A1:L3"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -757,7 +833,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74616A16-854D-4C81-B83A-6963E03D2814}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
